--- a/IMU_CALIBATION_ALL_DATA(AutoRecovered).xlsx
+++ b/IMU_CALIBATION_ALL_DATA(AutoRecovered).xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Desktop\Elu\Reaal\UT\UT_CALIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3310C8BA-47A1-4940-B618-344567A2BDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4EF9EE-287B-445F-8FAB-3F7EB4DE456C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{C4B1835E-1845-4776-B4ED-FF7E979FA931}"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" activeTab="2" xr2:uid="{C4B1835E-1845-4776-B4ED-FF7E979FA931}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="264">
   <si>
     <t>TEST DAY 1</t>
   </si>
@@ -487,21 +488,12 @@
     <t>python data_analysis_V3.py --file DATA/gyro_clean_movements.txt --accel-file DATA/manual1.txt</t>
   </si>
   <si>
-    <t>python gyrotest_parem.py --gyro-cal "1.75160508e-02 2.00000000e-01 2.29405639e-02 -1.56104886e-01 2.00000000e-01 -2.00000000e-01 9.41758628e-01 9.70617155e-01 9.80193644e-01 2.20863900e+00 1.05451400e+00 3.63871000e-01"</t>
-  </si>
-  <si>
     <t>python gyro_analysis_final.py --file DATA/gyro_clean_movements.txt --accel-params manual_accel_params.txt --units deg_s --rate 70</t>
   </si>
   <si>
-    <t>python gyrotest_parem.py --gyro-bias "2.20863900e+00 1.05451400e+00 3.63871000e-01" --gyro-scale "1.0399e+00 1.0399e+00 1.0399e+00"</t>
-  </si>
-  <si>
     <t>1.04195648e+00 1.02864937e+00 1.01523233e+00</t>
   </si>
   <si>
-    <t>python gyrotest_parem.py --gyro-bias "2.20863900e+00 1.05451400e+00 3.63871000e-01" --gyro-scale "1.04195648e+00 1.02864937e+00 1.01523233e+00"</t>
-  </si>
-  <si>
     <t>2.20863900e+00 1.05451400e+00 3.63871000e-01 1.04188778e+00 1.02808295e+00 1.01339930e+00 -5.44009805e-04 2.75603200e-03 5.95177417e-04 1.86572268e-03 -1.34887544e-03 -1.59615810e-03</t>
   </si>
   <si>
@@ -512,6 +504,333 @@
   </si>
   <si>
     <t>TURNTABLE</t>
+  </si>
+  <si>
+    <t>python data_analysis_V3.py --file DATA/gyro_clean_movements.txt --accel-file DATA/guided1.txt</t>
+  </si>
+  <si>
+    <t>9.29249338e-01 1.02539725e+00 1.00016388e+00</t>
+  </si>
+  <si>
+    <t>python data_analysis_V3.py --file DATA/gyro_clean_movements.txt --accel-file DATA/TURNTABLE1_ACCEL.txt</t>
+  </si>
+  <si>
+    <t>=== Before gyro capython adflsh2.py --file DATA/gyro_clean_movements.txt --accel-file DATA/TURNTABLE1_ACCEL.txtlibration ===</t>
+  </si>
+  <si>
+    <t>Segment 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  start accel line: 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end   accel line: 485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 raw : [-0.06496761  0.06976744  9.85693101]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 raw : [-0.47364635 -0.41693679 -9.75650887]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 unit: [-0.006591  0.007078  0.999953]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 unit: [-0.048445 -0.042645 -0.997915]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  accel angle               : 176.242985 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 173.928296 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 173.909676 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err :  9.638557 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro samples in segment   : 476</t>
+  </si>
+  <si>
+    <t>Segment 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  start accel line: 485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end   accel line: 1107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 raw : [-0.47364635 -0.41693679 -9.75650887]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 raw : [ 9.80301937  0.16850412 -0.04119514]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 unit: [-0.048445 -0.042645 -0.997915]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 unit: [ 0.999843  0.017186 -0.004202]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  accel angle               : 92.577916 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 89.105753 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 89.043914 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err : 171.619829 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro samples in segment   : 617</t>
+  </si>
+  <si>
+    <t>Segment 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  start accel line: 1107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end   accel line: 1604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 raw : [ 9.80301937  0.16850412 -0.04119514]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 raw : [-9.83829832 -0.09690262 -0.06647771]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 unit: [ 0.999843  0.017186 -0.004202]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 unit: [-0.999929 -0.009849 -0.006757]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  accel angle               : 179.244368 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 177.764960 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 177.348400 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err :  1.596678 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro samples in segment   : 492</t>
+  </si>
+  <si>
+    <t>Segment 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  start accel line: 1604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end   accel line: 2212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 raw : [-9.83829832 -0.09690262 -0.06647771]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 raw : [ 9.80714595  0.08231479 -0.04702958]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 unit: [-0.999929 -0.009849 -0.006757]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 unit: [ 0.999953  0.008393 -0.004795]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  accel angle               : 179.332891 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 178.057154 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 178.551551 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err :  2.186397 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro samples in segment   : 603</t>
+  </si>
+  <si>
+    <t>Segment 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  start accel line: 2745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end   accel line: 3089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 raw : [0.03497894 0.08253175 9.84428972]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 raw : [-0.14231694  9.81491981 -0.24831774]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 unit: [0.003553 0.008383 0.999959]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 unit: [-0.014494  0.999575 -0.025289]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  accel angle               : 90.971778 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 89.005986 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 89.146205 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err : 177.048257 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro samples in segment   : 339</t>
+  </si>
+  <si>
+    <t>Segment 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  start accel line: 3089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end   accel line: 3617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 raw : [-0.14231694  9.81491981 -0.24831774]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 raw : [ 9.80339752  0.08930925 -0.10537397]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a0 unit: [-0.014494  0.999575 -0.025289]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  a1 unit: [ 0.999901  0.009109 -0.010748]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  accel angle               : 90.293092 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 85.776021 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 85.788447 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err : 173.080725 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro samples in segment   : 523</t>
+  </si>
+  <si>
+    <t>=== After gyro calibration ===</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 180.901268 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 180.968283 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err :  2.871674 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 92.098874 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 92.036452 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err : 170.923235 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 181.126336 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 180.715505 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err :  1.825420 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 179.398532 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 179.842725 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err :  0.770575 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 91.952604 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 92.105396 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err : 175.109914 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro integrated angle(q)  : 87.803227 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gyro path angle(sum wdT)  : 87.817984 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  end-vector prediction err : 177.934961 deg</t>
+  </si>
+  <si>
+    <t>Prediction error summary:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  mean   : 88.239296 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  median : 86.897455 deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  max    : 177.934961 deg</t>
+  </si>
+  <si>
+    <t>python gyrotest_final.py --gyro-bias "2.20863900e+00 1.05451400e+00 3.63871000e-01" --gyro-scale "1.0399e+00 1.0399e+00 1.0399e+00"</t>
+  </si>
+  <si>
+    <t>python gyrotest_final.py --gyro-cal "1.75160508e-02 2.00000000e-01 2.29405639e-02 -1.56104886e-01 2.00000000e-01 -2.00000000e-01 9.41758628e-01 9.70617155e-01 9.80193644e-01 2.20863900e+00 1.05451400e+00 3.63871000e-01"</t>
+  </si>
+  <si>
+    <t>python gyrotest_final.py --gyro-bias "2.20863900e+00 1.05451400e+00 3.63871000e-01" --gyro-scale "1.04195648e+00 1.02864937e+00 1.01523233e+00"</t>
+  </si>
+  <si>
+    <t>python gyrotest_final.py --gyro-bias "2.20863900e+00 1.05451400e+00 3.63871000e-01" --gyro-scale "9.29249338e-01 1.02539725e+00 1.00016388e+00"</t>
+  </si>
+  <si>
+    <t>python gyrotest_final.py --gyro-bias "2.20863900e+00 1.05451400e+00 3.63871000e-01" --gyro-scale "8.25532851e-01 1.04201770e+00 1.02240288e+00"</t>
+  </si>
+  <si>
+    <t>python data_analysis_final.py --file DATA/gyro_clean_movements.txt --accel-file DATA/TURNTABLE1_ACCEL.txt</t>
+  </si>
+  <si>
+    <t>python data_analysis_final.py --file DATA/gyro_clean_movements.txt --accel-file DATA/manual1.txt</t>
+  </si>
+  <si>
+    <t>python data_analysis_final.py --file DATA/gyro_clean_movements.txt --accel-file DATA/guided1.txt</t>
+  </si>
+  <si>
+    <t>python data_analysis_final.py ---file DATA/guided1.txt</t>
+  </si>
+  <si>
+    <t>python gyrotest_final.py --gyro-cal "-4.064292e-03 -4.383641e-03 -4.859623e-03 -5.952036e-03 2.386640e-02 -4.852485e-03 1.016405e+00 1.018756e+00 1.018576e+00 2.208639e+00 1.054514e+00 3.638710e-01"</t>
   </si>
 </sst>
 </file>
@@ -1853,57 +2172,724 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51998A20-1D4F-419C-8A91-2974B471845E}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="C17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="C18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="C20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="C21" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="C22" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="C24" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="C25" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="C27" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>263</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8F75958-E88D-4414-A904-37B6255106ED}">
+  <dimension ref="A1:G84"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
+        <v>161</v>
+      </c>
+      <c r="G5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>162</v>
+      </c>
+      <c r="G6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
+        <v>163</v>
+      </c>
+      <c r="G7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
+        <v>165</v>
+      </c>
+      <c r="G9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>166</v>
+      </c>
+      <c r="G10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
+        <v>167</v>
+      </c>
+      <c r="G11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
+        <v>169</v>
+      </c>
+      <c r="G13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
+        <v>170</v>
+      </c>
+      <c r="G14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
+        <v>171</v>
+      </c>
+      <c r="G16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>172</v>
+      </c>
+      <c r="G17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>173</v>
+      </c>
+      <c r="G18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>157</v>
+        <v>174</v>
+      </c>
+      <c r="G19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>176</v>
+      </c>
+      <c r="G21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>177</v>
+      </c>
+      <c r="G22" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>178</v>
+      </c>
+      <c r="G23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>179</v>
+      </c>
+      <c r="G24" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>180</v>
+      </c>
+      <c r="G25" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>181</v>
+      </c>
+      <c r="G26" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>182</v>
+      </c>
+      <c r="G27" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>183</v>
+      </c>
+      <c r="G29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>184</v>
+      </c>
+      <c r="G30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>185</v>
+      </c>
+      <c r="G31" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>186</v>
+      </c>
+      <c r="G32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>188</v>
+      </c>
+      <c r="G34" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>189</v>
+      </c>
+      <c r="G35" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>190</v>
+      </c>
+      <c r="G36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>191</v>
+      </c>
+      <c r="G37" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>192</v>
+      </c>
+      <c r="G38" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>193</v>
+      </c>
+      <c r="G39" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>194</v>
+      </c>
+      <c r="G40" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>195</v>
+      </c>
+      <c r="G42" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>196</v>
+      </c>
+      <c r="G43" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>197</v>
+      </c>
+      <c r="G44" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>198</v>
+      </c>
+      <c r="G45" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>199</v>
+      </c>
+      <c r="G46" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>200</v>
+      </c>
+      <c r="G47" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>201</v>
+      </c>
+      <c r="G48" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>202</v>
+      </c>
+      <c r="G49" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>203</v>
+      </c>
+      <c r="G50" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>204</v>
+      </c>
+      <c r="G51" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>205</v>
+      </c>
+      <c r="G52" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>206</v>
+      </c>
+      <c r="G53" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>207</v>
+      </c>
+      <c r="G55" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>208</v>
+      </c>
+      <c r="G56" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>209</v>
+      </c>
+      <c r="G57" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>210</v>
+      </c>
+      <c r="G58" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>211</v>
+      </c>
+      <c r="G59" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>212</v>
+      </c>
+      <c r="G60" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>213</v>
+      </c>
+      <c r="G61" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>214</v>
+      </c>
+      <c r="G62" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>215</v>
+      </c>
+      <c r="G63" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>216</v>
+      </c>
+      <c r="G64" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>217</v>
+      </c>
+      <c r="G65" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>218</v>
+      </c>
+      <c r="G66" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>219</v>
+      </c>
+      <c r="G68" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>220</v>
+      </c>
+      <c r="G69" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>221</v>
+      </c>
+      <c r="G70" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>222</v>
+      </c>
+      <c r="G71" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>223</v>
+      </c>
+      <c r="G72" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>224</v>
+      </c>
+      <c r="G73" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>225</v>
+      </c>
+      <c r="G74" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>226</v>
+      </c>
+      <c r="G75" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>227</v>
+      </c>
+      <c r="G76" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>228</v>
+      </c>
+      <c r="G77" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>229</v>
+      </c>
+      <c r="G78" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>230</v>
+      </c>
+      <c r="G79" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="81" spans="7:7">
+      <c r="G81" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="82" spans="7:7">
+      <c r="G82" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="83" spans="7:7">
+      <c r="G83" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="84" spans="7:7">
+      <c r="G84" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
